--- a/PCB/Lattice PCB/BOM FPGA_DENDY LAT.xlsx
+++ b/PCB/Lattice PCB/BOM FPGA_DENDY LAT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="105" windowWidth="25875" windowHeight="11310"/>
+    <workbookView xWindow="360" yWindow="165" windowWidth="25875" windowHeight="11250"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="117">
   <si>
     <t>SN74LVC8T245PWR</t>
   </si>
@@ -359,6 +359,15 @@
   </si>
   <si>
     <t>2,1х5.5x9mm</t>
+  </si>
+  <si>
+    <t>crystal oscillator  14.318MHz</t>
+  </si>
+  <si>
+    <t>7050</t>
+  </si>
+  <si>
+    <t>crystal oscillator  17.734MHz</t>
   </si>
 </sst>
 </file>
@@ -4543,7 +4552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:U57"/>
+  <dimension ref="A4:U59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -4934,20 +4943,16 @@
       <c r="B19" s="40"/>
       <c r="C19" s="40"/>
       <c r="D19" s="40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>44</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="F19" s="40"/>
       <c r="G19" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" s="43" t="s">
-        <v>109</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="H19" s="43"/>
       <c r="I19" s="43"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44"/>
@@ -4962,127 +4967,123 @@
       <c r="T19" s="44"/>
       <c r="U19" s="44"/>
     </row>
-    <row r="20" spans="1:21" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="42" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="40">
+        <v>1</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="44"/>
+    </row>
+    <row r="21" spans="1:21" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="40"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40">
+        <v>2</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="I21" s="43"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+    </row>
+    <row r="22" spans="1:21" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="40"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E22" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="42" t="s">
+      <c r="F22" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G22" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="42" t="s">
+      <c r="H22" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="39"/>
-      <c r="U20" s="41"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1206</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1">
-        <v>6</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="41"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
-        <v>11</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I23" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1206</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -5101,31 +5102,43 @@
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>59</v>
+        <v>6</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H24" s="20" t="s">
-        <v>58</v>
+      <c r="H24" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="I24" s="6"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>53</v>
@@ -5133,72 +5146,64 @@
       <c r="G25" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="H25" s="20" t="s">
-        <v>60</v>
+      <c r="H25" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="I25" s="6"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>68</v>
+        <v>53</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="I27" s="6"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -5208,7 +5213,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>19</v>
@@ -5217,7 +5222,7 @@
         <v>11</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="5"/>
@@ -5231,46 +5236,46 @@
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
     </row>
-    <row r="29" spans="1:21" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="40"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="F29" s="40" t="s">
+      <c r="E29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="42" t="s">
+      <c r="G29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="I29" s="43"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
+      <c r="H29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I29" s="6"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>19</v>
@@ -5279,7 +5284,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="5"/>
@@ -5293,55 +5298,55 @@
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="1" t="s">
+    <row r="31" spans="1:21" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40">
+        <v>2</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I31" s="6"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
+      <c r="H31" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="I31" s="43"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="42"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="42"/>
+      <c r="S31" s="42"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="5"/>
@@ -5360,19 +5365,19 @@
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
-        <v>9</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>71</v>
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="5"/>
@@ -5393,8 +5398,8 @@
       <c r="D34" s="1">
         <v>3</v>
       </c>
-      <c r="E34" s="12" t="s">
-        <v>72</v>
+      <c r="E34" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>73</v>
@@ -5403,7 +5408,7 @@
         <v>11</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="5"/>
@@ -5422,10 +5427,10 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>73</v>
@@ -5434,7 +5439,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="5"/>
@@ -5449,11 +5454,14 @@
       <c r="S35" s="5"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>73</v>
@@ -5461,28 +5469,39 @@
       <c r="G36" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="H36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36" s="6"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>11</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="5"/>
@@ -5497,214 +5516,205 @@
       <c r="S37" s="5"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
       <c r="D38" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="I38" s="6"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
+      <c r="H38" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>85</v>
+      <c r="H39" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="I39" s="6"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="35" t="s">
-        <v>87</v>
+      <c r="H40" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="I40" s="6"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="C41" s="1"/>
       <c r="D41" s="1">
-        <v>41</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="H41" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" s="6"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>26</v>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="14"/>
-      <c r="U42" s="2"/>
+      <c r="H42" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="I42" s="6"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
       <c r="D43" s="1">
-        <v>8</v>
-      </c>
-      <c r="E43" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="F43" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I43" s="6"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
+      <c r="G43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C44" s="7"/>
-      <c r="D44" s="5" t="s">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="25" t="s">
-        <v>104</v>
+      <c r="E44" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I44" s="13"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" s="14"/>
+      <c r="U44" s="2"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="F45" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="I45" s="6"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
@@ -5717,56 +5727,52 @@
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
     </row>
-    <row r="46" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="C46" s="24"/>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C46" s="7"/>
       <c r="D46" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="I46" s="6"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="U46" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I46" s="13"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
     </row>
-    <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
-      <c r="D47" s="5" t="s">
-        <v>12</v>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1">
+        <v>1</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I47" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="6"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
@@ -5777,17 +5783,26 @@
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
-      <c r="U47" s="2"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" s="6"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
@@ -5800,14 +5815,24 @@
       <c r="S48" s="5"/>
       <c r="U48" s="2"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
+      <c r="D49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
@@ -5822,9 +5847,11 @@
       <c r="U49" s="2"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="22"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="23"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -5841,6 +5868,8 @@
       <c r="U50" s="2"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="23"/>
@@ -5861,8 +5890,8 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="23"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="22"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -5876,68 +5905,66 @@
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
+      <c r="U52" s="2"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="U53" s="2"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C54" s="4"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="5"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C55" s="4"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="4"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="D56" s="8"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -5958,22 +5985,62 @@
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C57" s="4"/>
       <c r="D57" s="7"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7"/>
+      <c r="S57" s="7"/>
       <c r="T57" s="4"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C59" s="4"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
